--- a/data/登場角色清單demo檔.xlsx
+++ b/data/登場角色清單demo檔.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\GSheet\我當校長超勇的\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\我當校長超勇的\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDA6D686-F089-48C3-B04D-1E2A84D986E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC7F4C44-4085-466B-9936-DF43BFFD4E45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6710" yWindow="1780" windowWidth="25880" windowHeight="18890" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9370" yWindow="1990" windowWidth="25880" windowHeight="18890" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="登場角色清單" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="67">
   <si>
     <t>當前居民親密度</t>
   </si>
@@ -224,9 +224,6 @@
   </si>
   <si>
     <t>肖國才</t>
-  </si>
-  <si>
-    <t>0%</t>
   </si>
 </sst>
 </file>
@@ -492,7 +489,6 @@
     <xf numFmtId="0" fontId="9" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -503,6 +499,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -844,7 +843,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:I32"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="18.81640625" customWidth="1"/>
@@ -857,40 +856,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="C1" s="8"/>
+      <c r="B1" s="12">
+        <v>0</v>
+      </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="10">
+      <c r="B2" s="9">
         <v>240000</v>
       </c>
-      <c r="C2" s="8"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A3" s="9" t="s">
+      <c r="A3" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="10">
-        <v>1300</v>
-      </c>
-      <c r="C3" s="8"/>
+      <c r="B3" s="9">
+        <v>1800</v>
+      </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A6" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" s="9" t="s">
+      <c r="A6" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="C6" s="8" t="s">
         <v>5</v>
       </c>
       <c r="E6" s="1" t="s">
@@ -908,10 +904,10 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7" s="11" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="B7" s="11">
-        <v>75504</v>
+        <v>96814</v>
       </c>
       <c r="C7" s="11">
         <v>3</v>
@@ -930,13 +926,13 @@
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A8" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="B8" s="11">
-        <v>59491</v>
-      </c>
-      <c r="C8" s="11">
+      <c r="A8" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="B8" s="10">
+        <v>86555</v>
+      </c>
+      <c r="C8" s="10">
         <v>3</v>
       </c>
       <c r="E8" s="5" t="s">
@@ -953,13 +949,13 @@
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A9" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="B9" s="12">
-        <v>58961</v>
-      </c>
-      <c r="C9" s="12">
+      <c r="A9" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="11">
+        <v>67481</v>
+      </c>
+      <c r="C9" s="11">
         <v>3</v>
       </c>
       <c r="E9" s="5" t="s">
@@ -976,13 +972,13 @@
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A10" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="B10" s="12">
-        <v>51843</v>
-      </c>
-      <c r="C10" s="12">
+      <c r="A10" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="B10" s="10">
+        <v>59633</v>
+      </c>
+      <c r="C10" s="10">
         <v>3</v>
       </c>
       <c r="E10" s="5" t="s">
@@ -999,13 +995,13 @@
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A11" s="11" t="s">
+      <c r="A11" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="B11" s="11">
-        <v>49470</v>
-      </c>
-      <c r="C11" s="11">
+      <c r="B11" s="10">
+        <v>49582</v>
+      </c>
+      <c r="C11" s="10">
         <v>3</v>
       </c>
       <c r="E11" s="5" t="s">
@@ -1022,13 +1018,13 @@
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A12" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="B12" s="11">
-        <v>42572</v>
-      </c>
-      <c r="C12" s="11">
+      <c r="A12" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="B12" s="10">
+        <v>46753</v>
+      </c>
+      <c r="C12" s="10">
         <v>3</v>
       </c>
       <c r="E12" s="5" t="s">
@@ -1046,10 +1042,10 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A13" s="11" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="B13" s="11">
-        <v>42250</v>
+        <v>45300</v>
       </c>
       <c r="C13" s="11">
         <v>3</v>
@@ -1069,10 +1065,10 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A14" s="11" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B14" s="11">
-        <v>42165</v>
+        <v>43303</v>
       </c>
       <c r="C14" s="11">
         <v>3</v>
@@ -1091,13 +1087,13 @@
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A15" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="B15" s="12">
-        <v>39896</v>
-      </c>
-      <c r="C15" s="12">
+      <c r="A15" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="B15" s="10">
+        <v>42684</v>
+      </c>
+      <c r="C15" s="10">
         <v>3</v>
       </c>
       <c r="E15" s="5" t="s">
@@ -1114,13 +1110,13 @@
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A16" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="B16" s="12">
-        <v>39635</v>
-      </c>
-      <c r="C16" s="12">
+      <c r="A16" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" s="10">
+        <v>42277</v>
+      </c>
+      <c r="C16" s="10">
         <v>3</v>
       </c>
       <c r="E16" s="5" t="s">
@@ -1137,13 +1133,13 @@
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A17" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="B17" s="12">
-        <v>37145</v>
-      </c>
-      <c r="C17" s="12">
+      <c r="A17" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="B17" s="11">
+        <v>40247</v>
+      </c>
+      <c r="C17" s="11">
         <v>3</v>
       </c>
       <c r="E17" s="5" t="s">
@@ -1160,13 +1156,13 @@
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A18" s="11" t="s">
+      <c r="A18" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="B18" s="11">
-        <v>36840</v>
-      </c>
-      <c r="C18" s="11">
+      <c r="B18" s="10">
+        <v>36952</v>
+      </c>
+      <c r="C18" s="10">
         <v>3</v>
       </c>
       <c r="E18" s="5" t="s">
@@ -1183,13 +1179,13 @@
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A19" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="B19" s="12">
-        <v>26924</v>
-      </c>
-      <c r="C19" s="12">
+      <c r="A19" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B19" s="10">
+        <v>36360</v>
+      </c>
+      <c r="C19" s="10">
         <v>3</v>
       </c>
       <c r="E19" s="5" t="s">
@@ -1207,10 +1203,10 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A20" s="11" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="B20" s="11">
-        <v>15432</v>
+        <v>27036</v>
       </c>
       <c r="C20" s="11">
         <v>3</v>
@@ -1224,10 +1220,10 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A21" s="11" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="B21" s="11">
-        <v>15026</v>
+        <v>17352</v>
       </c>
       <c r="C21" s="11">
         <v>3</v>
@@ -1240,13 +1236,13 @@
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A22" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="B22" s="12">
-        <v>13553</v>
-      </c>
-      <c r="C22" s="12">
+      <c r="A22" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="B22" s="10">
+        <v>16916</v>
+      </c>
+      <c r="C22" s="10">
         <v>3</v>
       </c>
       <c r="H22" s="5" t="s">
@@ -1254,101 +1250,112 @@
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A23" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="B23" s="12">
-        <v>13139</v>
-      </c>
-      <c r="C23" s="12">
+      <c r="A23" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="B23" s="10">
+        <v>15544</v>
+      </c>
+      <c r="C23" s="10">
         <v>3</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A24" s="12" t="s">
+      <c r="A24" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="B24" s="11">
+        <v>13665</v>
+      </c>
+      <c r="C24" s="11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A25" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="B24" s="12">
-        <v>10642</v>
-      </c>
-      <c r="C24" s="12">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A25" s="12" t="s">
+      <c r="B25" s="11">
+        <v>10754</v>
+      </c>
+      <c r="C25" s="11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A26" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="B25" s="12">
-        <v>9677</v>
-      </c>
-      <c r="C25" s="12">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A26" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="B26" s="12">
-        <v>8496</v>
-      </c>
-      <c r="C26" s="12">
+      <c r="B26" s="11">
+        <v>9789</v>
+      </c>
+      <c r="C26" s="11">
         <v>3</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A27" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="B27" s="11">
+        <v>8628</v>
+      </c>
+      <c r="C27" s="11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A28" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="B27" s="11">
-        <v>7403</v>
-      </c>
-      <c r="C27" s="11">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A28" s="11" t="s">
+      <c r="B28" s="10">
+        <v>7515</v>
+      </c>
+      <c r="C28" s="10">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A29" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="B28" s="11">
-        <v>5467</v>
-      </c>
-      <c r="C28" s="11">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A29" s="11" t="s">
+      <c r="B29" s="10">
+        <v>5579</v>
+      </c>
+      <c r="C29" s="10">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A30" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="B29" s="11">
-        <v>5467</v>
-      </c>
-      <c r="C29" s="11">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A30" s="11" t="s">
+      <c r="B30" s="10">
+        <v>5579</v>
+      </c>
+      <c r="C30" s="10">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A31" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="B30" s="11">
-        <v>5205</v>
-      </c>
-      <c r="C30" s="11">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A31" s="11" t="s">
+      <c r="B31" s="10">
+        <v>5317</v>
+      </c>
+      <c r="C31" s="10">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A32" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="B31" s="11">
-        <v>4936</v>
-      </c>
-      <c r="C31" s="11">
+      <c r="B32" s="10">
+        <v>5048</v>
+      </c>
+      <c r="C32" s="10">
         <v>3</v>
       </c>
     </row>
